--- a/QCM4_1_CH.xlsx
+++ b/QCM4_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD10D8E-BBDB-4D67-9376-1ABB389FAFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25336C12-B2C4-47C9-BF84-B4D2CE3429FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="246">
   <si>
     <t>Question</t>
   </si>
@@ -179,19 +179,7 @@
     <t>Butanoate de méthyl-propyle</t>
   </si>
   <si>
-    <t>Option A (Saponification / Hydrolyse basique)</t>
-  </si>
-  <si>
     <t>Option B (Estérification)</t>
-  </si>
-  <si>
-    <t>Option C (Hydrolyse)</t>
-  </si>
-  <si>
-    <t>Option A</t>
-  </si>
-  <si>
-    <t>Option B</t>
   </si>
   <si>
     <t>Option C</t>
@@ -574,126 +562,6 @@
   <si>
     <t>Cette molécule est :
 R — OH</t>
-  </si>
-  <si>
-    <t>Cette molécule est :
-    O
-   //
-R — C
-   \
-    OH</t>
-  </si>
-  <si>
-    <t>Cette molécule est :
-    O
-   //
-R — C
-   \
-    O — R'</t>
-  </si>
-  <si>
-    <t>Cette molécule est :
-    O
-   //
-R — C
-   \
-    O⁻</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule est :
-CH₃ — CH — CH₂ — CH₃
-      |
-      OH</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule est :
-CH₃ — CH — CH — CH₃
-      |    |
-      CH₃  OH</t>
-  </si>
-  <si>
-    <t>La classe de cet alcool est :
-CH₃ — CH₂ — OH</t>
-  </si>
-  <si>
-    <t>La classe de cet alcool est :
-      CH₃
-      |
-CH₃ — C — CH₃
-      |
-      OH</t>
-  </si>
-  <si>
-    <t>La classe de cet alcool est :
-CH₃ — CH — CH₃
-      |
-      OH</t>
-  </si>
-  <si>
-    <t>La classe de cet alcool est :
-CH₃ — CH — CH₂ — CH₃
-      |
-      OH</t>
-  </si>
-  <si>
-    <t>La classe de cet alcool est :
-R — CH₂ — OH</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule :
-      O
-     //
-CH₃ — C
-     \
-      OH</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule :
-CH₃ — CH₂ — CH — CH₂ — C == O
-            |          |
-            CH₃        OH</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule est :
-            O
-           //
-CH₃ — CH₂ — C
-           \
-            O — CH₃</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule est :
-      CH₃   O
-      |    //
-CH₃ — CH — C
-           \
-            O — CH₃</t>
-  </si>
-  <si>
-    <t>Le nom de cette molécule est :
-                  O
-                 //
-CH₃ — CH₂ — CH₂ — C
-                 \
-                  O — CH — CH₃
-                      |
-                      CH₃</t>
-  </si>
-  <si>
-    <t>Parmi les équations-bilan suivantes, laquelle est celle d'une réaction d'estérification ?
-    O                       O
-   //                      //
-R—C    +  R'—OH   ====  R—C      +  H₂O
-   \\                       \
-    OH                      O—R'</t>
-  </si>
-  <si>
-    <t>Parmi les équations-bilan suivantes, laquelle est celle d'une réaction d'hydrolyse ?
-    O                       O
-   //                      //
-R—C    +  H₂O     ====  R—C      +  R'—OH
-   \\                       \
-    O—R'                    OH</t>
   </si>
   <si>
     <t>Quel est le catalyseur habituel de la réaction d'estérification ?</t>
@@ -826,42 +694,6 @@
     <t>&lt;center&gt;&lt;b&gt;L'acide acétique (éthanoïque)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 La réaction entre l'acide acétique et l'éthanol a un taux d'avancement à l'équilibre de 67% lorsque les réactifs sont en proportions stœchiométriques (mélange équimolaire dans le cas de cette réaction).
 &lt;br&gt;Données : x² - 4x + 8/3 = (x - 0,85)(x - 3,15) ; $\quad$ (0,67 / 0,33)² = 4</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;L'aspartame&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-L'aspartame est un édulcorant utilisé en remplacement du saccharose (sucre) dans l'agroalimentaire. Sa formule topologique est la suivante :
-    O                   O                 O
-   //                  //                //
-HO — C — CH₂ — CH — C — NH — CH — C — O — CH₃
-               |    ||       |
-               NH₂  O        CH₂ — [ C₆H₅ ] (Cycle benzénique)
-&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(N)=14 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Le gallate de propyle&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Le gallate de propyle est un antioxydant utilisé comme additif alimentaire sous le numéro E310. C'est un ester formé à partir de l'acide gallique. On réalise un mélange d'une mole d'acide gallique et d'une mole d'alcool B. Après addition d'acide sulfurique concentré, le mélange est chauffé à reflux pendant une heure. On obtient 106 g de gallate de propyle dont la formule semi-développée est :
-      OH
-      |
-HO — [C₆H₂] — C — O — CH₂ — CH₂ — CH₃
-      |       ||
-      OH      O
-&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La butyrine&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-La butyrine est l'un des corps gras contenus dans le beurre. La dégradation de la butyrine produit de l'acide butyrique dont le goût et l'odeur désagréables sont caractéristiques du beurre rance. La formule semi-développée de la butyrine est :
-      O
-     //
-CH₂ — O — C — CH₂ — CH₂ — CH₃
-|
-|     O
-|    //
-CH  — O — C — CH₂ — CH₂ — CH₃
-|
-|     O
-|    //
-CH₂ — O — C — CH₂ — CH₂ — CH₃
-&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
   </si>
   <si>
     <t>On fait réagir une mole de butyrine avec un excès de potasse (K⁺(aq) + HO⁻(aq)) concentrée. Après 30 minutes de chauffage, on observe, après relargage, la formation d'un précipité jaune de butanoate de potassium. Après filtration, rinçage et séchage, la masse de précipité est égale à 126 g.
@@ -888,6 +720,84 @@
   </si>
   <si>
     <t>CH_QCM4_1_Q3.png</t>
+  </si>
+  <si>
+    <t>Parmi les équations-bilan suivantes, laquelle est celle d'une réaction d'estérification ?</t>
+  </si>
+  <si>
+    <t>Parmi les équations-bilan suivantes, laquelle est celle d'une réaction d'hydrolyse ?</t>
+  </si>
+  <si>
+    <t>Cette molécule &lt;img src="/images/FC_Q149.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Cette molécule &lt;img src="/images/FC_Q150.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Cette molécule &lt;img src="/images/FC_Q151.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q152.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q153.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>La classe de cet alcool &lt;img src="/images/FC_Q154.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>La classe de cet alcool &lt;img src="/images/FC_Q155.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>La classe de cet alcool &lt;img src="/images/FC_Q156.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>La classe de cet alcool &lt;img src="/images/FC_Q157.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>La classe de cet alcool &lt;img src="/images/FC_Q158.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q159.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est:</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q160.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est:</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q161.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q162.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>Le nom de cette molécule &lt;img src="/images/FC_Q163.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est :</t>
+  </si>
+  <si>
+    <t>&lt;img src="/images/FC_Q164A.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;img src="/images/FC_Q164B.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;img src="/images/FC_Q164C.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;L'aspartame&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+L'aspartame est un édulcorant utilisé en remplacement du saccharose (sucre) dans l'agroalimentaire. Sa formule topologique est la suivante :
+&lt;img src="/images/FC_Q169.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(N)=14 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Le gallate de propyle&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Le gallate de propyle est un antioxydant utilisé comme additif alimentaire sous le numéro E310. C'est un ester formé à partir de l'acide gallique. On réalise un mélange d'une mole d'acide gallique et d'une mole d'alcool B. Après addition d'acide sulfurique concentré, le mélange est chauffé à reflux pendant une heure. On obtient 106 g de gallate de propyle dont la formule semi-développée est :
+&lt;img src="/images/FC_Q171.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La butyrine&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+La butyrine est l'un des corps gras contenus dans le beurre. La dégradation de la butyrine produit de l'acide butyrique dont le goût et l'odeur désagréables sont caractéristiques du beurre rance. La formule semi-développée de la butyrine est :
+&lt;img src="/images/FC_Q175.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
   </si>
 </sst>
 </file>
@@ -1488,12 +1398,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="181.5" customHeight="1">
+    <row r="2" spans="1:11" ht="42.75" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>3</v>
@@ -1517,10 +1427,10 @@
       <c r="J2" s="4"/>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="89.25">
+    <row r="3" spans="1:11" ht="25.5">
       <c r="A3" s="15"/>
       <c r="B3" s="20" t="s">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>3</v>
@@ -1544,10 +1454,10 @@
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="89.25">
+    <row r="4" spans="1:11" ht="25.5">
       <c r="A4" s="15"/>
       <c r="B4" s="20" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>3</v>
@@ -1571,10 +1481,10 @@
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="89.25">
+    <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="15"/>
       <c r="B5" s="20" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>3</v>
@@ -1598,10 +1508,10 @@
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="63.75">
+    <row r="6" spans="1:11" ht="38.25">
       <c r="A6" s="15"/>
       <c r="B6" s="20" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>3</v>
@@ -1627,10 +1537,10 @@
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="63.75">
+    <row r="7" spans="1:11" ht="38.25">
       <c r="A7" s="15"/>
       <c r="B7" s="20" t="s">
-        <v>183</v>
+        <v>229</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>3</v>
@@ -1659,7 +1569,7 @@
     <row r="8" spans="1:11" ht="38.25">
       <c r="A8" s="15"/>
       <c r="B8" s="20" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>3</v>
@@ -1683,10 +1593,10 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="89.25">
+    <row r="9" spans="1:11" ht="38.25">
       <c r="A9" s="15"/>
       <c r="B9" s="20" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>3</v>
@@ -1710,10 +1620,10 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="63.75">
+    <row r="10" spans="1:11" ht="38.25">
       <c r="A10" s="15"/>
       <c r="B10" s="20" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>3</v>
@@ -1737,10 +1647,10 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:11" ht="63.75">
+    <row r="11" spans="1:11" ht="38.25">
       <c r="A11" s="15"/>
       <c r="B11" s="20" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>3</v>
@@ -1767,7 +1677,7 @@
     <row r="12" spans="1:11" ht="38.25">
       <c r="A12" s="15"/>
       <c r="B12" s="20" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>3</v>
@@ -1791,10 +1701,10 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="89.25">
+    <row r="13" spans="1:11" ht="38.25">
       <c r="A13" s="15"/>
       <c r="B13" s="20" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>3</v>
@@ -1820,10 +1730,10 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:11" ht="63.75">
+    <row r="14" spans="1:11" ht="38.25">
       <c r="A14" s="15"/>
       <c r="B14" s="20" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>3</v>
@@ -1849,10 +1759,10 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="89.25">
+    <row r="15" spans="1:11" ht="38.25">
       <c r="A15" s="15"/>
       <c r="B15" s="20" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>3</v>
@@ -1876,10 +1786,10 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:11" ht="89.25">
+    <row r="16" spans="1:11" ht="38.25">
       <c r="A16" s="15"/>
       <c r="B16" s="20" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
@@ -1903,10 +1813,10 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="114.75">
+    <row r="17" spans="1:9" ht="38.25">
       <c r="A17" s="15"/>
       <c r="B17" s="20" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
@@ -1928,555 +1838,555 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="102">
+    <row r="18" spans="1:9" ht="42.75">
       <c r="A18" s="11" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="102">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="42.75">
       <c r="A19" s="15"/>
       <c r="B19" s="20" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>52</v>
+      <c r="D19" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>242</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="42.75">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="114">
       <c r="A21" s="11" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.5">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.5">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="42.75">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="114.75">
+      <c r="A25" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="191.25">
-      <c r="A25" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="G25" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="178.5">
+      <c r="A27" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="242.25">
-      <c r="A27" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>82</v>
-      </c>
       <c r="F27" s="14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="28.5">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="15"/>
       <c r="B29" s="16" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="15"/>
       <c r="B30" s="16" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H30" s="18"/>
       <c r="I30" s="18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="140.25">
+      <c r="A31" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="280.5">
-      <c r="A31" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="E31" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="99.75">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="28.5">
       <c r="A33" s="15"/>
       <c r="B33" s="16" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H34" s="18"/>
       <c r="I34" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="57">
       <c r="A35" s="11" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G38" s="18" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>12</v>
@@ -2488,419 +2398,419 @@
     </row>
     <row r="40" spans="1:10" ht="213.75">
       <c r="A40" s="11" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>12</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="28.5">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H41" s="18"/>
       <c r="I41" s="18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.5">
       <c r="A42" s="15"/>
       <c r="B42" s="16" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H42" s="18"/>
       <c r="I42" s="18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="171">
       <c r="A43" s="11" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J43" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="15"/>
       <c r="B44" s="16" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F44" s="18"/>
       <c r="G44" s="18" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H44" s="18"/>
       <c r="I44" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="15"/>
       <c r="B45" s="16" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="156.75">
       <c r="A46" s="11" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J46" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="42.75">
       <c r="A47" s="15"/>
       <c r="B47" s="16" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.5">
       <c r="A48" s="15"/>
       <c r="B48" s="16" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="18" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="28.5">
       <c r="A49" s="15"/>
       <c r="B49" s="16" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="114">
       <c r="A50" s="11" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J50" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="15"/>
       <c r="B51" s="16" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="15"/>
       <c r="B52" s="16" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H52" s="18"/>
       <c r="I52" s="18" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="15"/>
       <c r="B53" s="16" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H53" s="18"/>
       <c r="I53" s="18" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="128.25">
       <c r="A54" s="11" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H54" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>173</v>
-      </c>
       <c r="I54" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="15"/>
       <c r="B55" s="16" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:10">

--- a/QCM4_1_CH.xlsx
+++ b/QCM4_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25336C12-B2C4-47C9-BF84-B4D2CE3429FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D42B311-DA69-4ECC-A772-C788CE53D203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="247">
   <si>
     <t>Question</t>
   </si>
@@ -194,30 +194,12 @@
     <t>L'eau H2O</t>
   </si>
   <si>
-    <t>L'acide acétique (éthanoïque)</t>
-  </si>
-  <si>
     <t>l'éthanoate d'éthyle</t>
   </si>
   <si>
     <t>l'éthanoate de méthyle</t>
   </si>
   <si>
-    <t>le méthanoate de méthyle</t>
-  </si>
-  <si>
-    <t>le méthanoate d'éthyle</t>
-  </si>
-  <si>
-    <t>K = ([Acide]eq.[Alcool]eq) / ([Ester]eq.[eau]eq)</t>
-  </si>
-  <si>
-    <t>K = [Ester]eq / ([Acide]eq.[Alcool]eq)</t>
-  </si>
-  <si>
-    <t>K = [Ester]eq / [Acide]eq</t>
-  </si>
-  <si>
     <t>K = ([Ester]eq.[eau]eq) / ([Acide]eq.[Alcool]eq)</t>
   </si>
   <si>
@@ -380,15 +362,6 @@
     <t>le réactif spectateur</t>
   </si>
   <si>
-    <t>x_f = 1 mol.</t>
-  </si>
-  <si>
-    <t>x_f = 3 mol.</t>
-  </si>
-  <si>
-    <t>x_f = 5 mol.</t>
-  </si>
-  <si>
     <t>enzymatique</t>
   </si>
   <si>
@@ -560,10 +533,6 @@
     <t>75%</t>
   </si>
   <si>
-    <t>Cette molécule est :
-R — OH</t>
-  </si>
-  <si>
     <t>Quel est le catalyseur habituel de la réaction d'estérification ?</t>
   </si>
   <si>
@@ -667,14 +636,6 @@
   </si>
   <si>
     <t>Le pourcentage d'ester hydrolysé :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On réalise l'hydrolyse du butanoate d'éthyle en chauffant à 200°C un mélange de 5,0 mol d'eau et de 1,0 mol d'ester. Le volume du mélange est de 180 mL. Après 24 heures de réaction, on prélève un échantillon de 10 mL. On le refroidit et on le titre ensuite par une solution de soude à 2,0 mol.L⁻¹. L'équivalence acidobasique est atteinte pour un volume de base versé V_BE = 17,5 mL.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-L'étude d'un mélange équimolaire d'acide méthanoïque et de pentan-1-ol, placé sous reflux dans un chauffe-ballon, a permis de déterminer la quantité n_A d'acide méthanoïque restant au cours du temps. Le graphe obtenu (n_A(mmol) en fonction de t(h)) montre une décroissance de 600 mmol à environ 200 mmol.</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
@@ -689,11 +650,6 @@
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Nomenclature&lt;/b&gt;&lt;/center&gt;&lt;br&gt;</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;L'acide acétique (éthanoïque)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-La réaction entre l'acide acétique et l'éthanol a un taux d'avancement à l'équilibre de 67% lorsque les réactifs sont en proportions stœchiométriques (mélange équimolaire dans le cas de cette réaction).
-&lt;br&gt;Données : x² - 4x + 8/3 = (x - 0,85)(x - 3,15) ; $\quad$ (0,67 / 0,33)² = 4</t>
   </si>
   <si>
     <t>On fait réagir une mole de butyrine avec un excès de potasse (K⁺(aq) + HO⁻(aq)) concentrée. Après 30 minutes de chauffage, on observe, après relargage, la formation d'un précipité jaune de butanoate de potassium. Après filtration, rinçage et séchage, la masse de précipité est égale à 126 g.
@@ -798,6 +754,54 @@
 La butyrine est l'un des corps gras contenus dans le beurre. La dégradation de la butyrine produit de l'acide butyrique dont le goût et l'odeur désagréables sont caractéristiques du beurre rance. La formule semi-développée de la butyrine est :
 &lt;img src="/images/FC_Q175.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
+  </si>
+  <si>
+    <t>La molécule suivante :
+R — OH
+&lt;br&gt; est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;L'acide acétique (éthanoïque)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+La réaction entre l'acide acétique et l'éthanol a un taux d'avancement à l'équilibre de 67% lorsque les réactifs sont en proportions stœchiométriques (mélange équimolaire dans le cas de cette réaction).
+&lt;br&gt;Données : x² - 4x + $\frac{8}{3}$ = (x - 0,85)(x - 3,15) ; $\quad$ $\frac{0,67}{0,33} = 2$</t>
+  </si>
+  <si>
+    <t>méthanoate de méthyle</t>
+  </si>
+  <si>
+    <t>méthanoate d'éthyle</t>
+  </si>
+  <si>
+    <t>K = $\frac{[Acide]_eq.[Alcool]_eq}{[Ester]_eq.[eau]_eq}$</t>
+  </si>
+  <si>
+    <t>K = $\frac{[Ester]_eq.[eau]_eq}{[Acide]_eq.[Alcool]_eq}$</t>
+  </si>
+  <si>
+    <t>K = $\frac{[Ester]_eq}{[Acide]_eq.[Alcool]_eq}$</t>
+  </si>
+  <si>
+    <t>K = $\frac{[Ester]_eq}{[Acide]_eq}$</t>
+  </si>
+  <si>
+    <t>$x_f = 1 mol.$</t>
+  </si>
+  <si>
+    <t>$x_f = 3 mol.$</t>
+  </si>
+  <si>
+    <t>$x_f = 5 mol.$</t>
+  </si>
+  <si>
+    <t>$\approx 5 min$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+L'étude d'un mélange équimolaire d'acide méthanoïque et de pentan-1-ol, placé sous reflux dans un chauffe-ballon, a permis de déterminer la quantité $n_A$ d'acide méthanoïque restant au cours du temps. Le graphe obtenu ($n_A(mmol)$ en fonction de t(h)) montre une décroissance de 600 mmol à environ 200 mmol.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On réalise l'hydrolyse du butanoate d'éthyle en chauffant à 200°C un mélange de 5,0 mol d'eau et de 1,0 mol d'ester. Le volume du mélange est de 180 mL. Après 24 heures de réaction, on prélève un échantillon de 10 mL. On le refroidit et on le titre ensuite par une solution de soude à 2,0 mol.L⁻¹. L'équivalence acidobasique est atteinte pour un volume de base versé $V_BE = 17,5 mL.$</t>
   </si>
 </sst>
 </file>
@@ -1400,10 +1404,10 @@
     </row>
     <row r="2" spans="1:11" ht="42.75" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>3</v>
@@ -1430,7 +1434,7 @@
     <row r="3" spans="1:11" ht="25.5">
       <c r="A3" s="15"/>
       <c r="B3" s="20" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>3</v>
@@ -1457,7 +1461,7 @@
     <row r="4" spans="1:11" ht="25.5">
       <c r="A4" s="15"/>
       <c r="B4" s="20" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>3</v>
@@ -1484,7 +1488,7 @@
     <row r="5" spans="1:11" ht="25.5">
       <c r="A5" s="15"/>
       <c r="B5" s="20" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>3</v>
@@ -1511,7 +1515,7 @@
     <row r="6" spans="1:11" ht="38.25">
       <c r="A6" s="15"/>
       <c r="B6" s="20" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>3</v>
@@ -1540,7 +1544,7 @@
     <row r="7" spans="1:11" ht="38.25">
       <c r="A7" s="15"/>
       <c r="B7" s="20" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>3</v>
@@ -1569,7 +1573,7 @@
     <row r="8" spans="1:11" ht="38.25">
       <c r="A8" s="15"/>
       <c r="B8" s="20" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>3</v>
@@ -1596,7 +1600,7 @@
     <row r="9" spans="1:11" ht="38.25">
       <c r="A9" s="15"/>
       <c r="B9" s="20" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>3</v>
@@ -1623,7 +1627,7 @@
     <row r="10" spans="1:11" ht="38.25">
       <c r="A10" s="15"/>
       <c r="B10" s="20" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>3</v>
@@ -1650,7 +1654,7 @@
     <row r="11" spans="1:11" ht="38.25">
       <c r="A11" s="15"/>
       <c r="B11" s="20" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>3</v>
@@ -1677,7 +1681,7 @@
     <row r="12" spans="1:11" ht="38.25">
       <c r="A12" s="15"/>
       <c r="B12" s="20" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>3</v>
@@ -1704,7 +1708,7 @@
     <row r="13" spans="1:11" ht="38.25">
       <c r="A13" s="15"/>
       <c r="B13" s="20" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>3</v>
@@ -1733,7 +1737,7 @@
     <row r="14" spans="1:11" ht="38.25">
       <c r="A14" s="15"/>
       <c r="B14" s="20" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>3</v>
@@ -1762,7 +1766,7 @@
     <row r="15" spans="1:11" ht="38.25">
       <c r="A15" s="15"/>
       <c r="B15" s="20" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>3</v>
@@ -1789,7 +1793,7 @@
     <row r="16" spans="1:11" ht="38.25">
       <c r="A16" s="15"/>
       <c r="B16" s="20" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
@@ -1816,7 +1820,7 @@
     <row r="17" spans="1:9" ht="38.25">
       <c r="A17" s="15"/>
       <c r="B17" s="20" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
@@ -1840,22 +1844,22 @@
     </row>
     <row r="18" spans="1:9" ht="42.75">
       <c r="A18" s="11" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
@@ -1866,19 +1870,19 @@
     <row r="19" spans="1:9" ht="42.75">
       <c r="A19" s="15"/>
       <c r="B19" s="20" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
@@ -1889,7 +1893,7 @@
     <row r="20" spans="1:9" ht="42.75">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>3</v>
@@ -1903,9 +1907,7 @@
       <c r="F20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>52</v>
-      </c>
+      <c r="G20" s="18"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18" t="s">
         <v>50</v>
@@ -1913,480 +1915,480 @@
     </row>
     <row r="21" spans="1:9" ht="114">
       <c r="A21" s="11" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>54</v>
-      </c>
       <c r="F21" s="14" t="s">
-        <v>55</v>
+        <v>235</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>56</v>
+        <v>236</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="42.75">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>58</v>
+        <v>240</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.5">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="42.75">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="114.75">
       <c r="A25" s="21" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="178.5">
       <c r="A27" s="21" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="28.5">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="15"/>
       <c r="B29" s="16" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="15"/>
       <c r="B30" s="16" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H30" s="18"/>
       <c r="I30" s="18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="140.25">
       <c r="A31" s="21" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="99.75">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="28.5">
       <c r="A33" s="15"/>
       <c r="B33" s="16" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H34" s="18"/>
       <c r="I34" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="57">
       <c r="A35" s="11" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G38" s="18" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>116</v>
+        <v>243</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>12</v>
@@ -2398,419 +2400,421 @@
     </row>
     <row r="40" spans="1:10" ht="213.75">
       <c r="A40" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>12</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="28.5">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H41" s="18"/>
       <c r="I41" s="18" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.5">
       <c r="A42" s="15"/>
       <c r="B42" s="16" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H42" s="18"/>
       <c r="I42" s="18" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="171">
       <c r="A43" s="11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J43" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="15"/>
       <c r="B44" s="16" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" s="18"/>
+        <v>122</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>244</v>
+      </c>
       <c r="G44" s="18" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H44" s="18"/>
       <c r="I44" s="18" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="15"/>
       <c r="B45" s="16" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="156.75">
       <c r="A46" s="11" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J46" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="42.75">
       <c r="A47" s="15"/>
       <c r="B47" s="16" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="18" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.5">
       <c r="A48" s="15"/>
       <c r="B48" s="16" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="18" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="28.5">
       <c r="A49" s="15"/>
       <c r="B49" s="16" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="114">
       <c r="A50" s="11" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="J50" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="15"/>
       <c r="B51" s="16" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="15"/>
       <c r="B52" s="16" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="H52" s="18"/>
       <c r="I52" s="18" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="15"/>
       <c r="B53" s="16" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="H53" s="18"/>
       <c r="I53" s="18" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="128.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="142.5">
       <c r="A54" s="11" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="15"/>
       <c r="B55" s="16" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:10">

--- a/QCM4_1_CH.xlsx
+++ b/QCM4_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D42B311-DA69-4ECC-A772-C788CE53D203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F1A8C9-C224-4BEB-A1F8-5AD44F2C4584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,11 +756,6 @@
 &lt;br&gt;M(H)=1 g.mol⁻¹ ; $\quad$ M(C)=12 g.mol⁻¹ ; $\quad$ M(O)=16 g.mol⁻¹</t>
   </si>
   <si>
-    <t>La molécule suivante :
-R — OH
-&lt;br&gt; est :</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;L'acide acétique (éthanoïque)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 La réaction entre l'acide acétique et l'éthanol a un taux d'avancement à l'équilibre de 67% lorsque les réactifs sont en proportions stœchiométriques (mélange équimolaire dans le cas de cette réaction).
 &lt;br&gt;Données : x² - 4x + $\frac{8}{3}$ = (x - 0,85)(x - 3,15) ; $\quad$ $\frac{0,67}{0,33} = 2$</t>
@@ -802,6 +797,12 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;Un mélange équimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 On réalise l'hydrolyse du butanoate d'éthyle en chauffant à 200°C un mélange de 5,0 mol d'eau et de 1,0 mol d'ester. Le volume du mélange est de 180 mL. Après 24 heures de réaction, on prélève un échantillon de 10 mL. On le refroidit et on le titre ensuite par une solution de soude à 2,0 mol.L⁻¹. L'équivalence acidobasique est atteinte pour un volume de base versé $V_BE = 17,5 mL.$</t>
+  </si>
+  <si>
+    <t>La molécule suivante :
+R — OH
+&lt;br&gt; est :
+&lt;br&gt;\text{R}-\text{C}(=\text{O})-\text{O}-\text{R}' + \text{OH}^- \rightleftharpoons \text{R}-\text{C}(=\text{O})-\text{O}^- + \text{R}'-\text{OH}</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1408,7 @@
         <v>203</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>3</v>
@@ -1915,7 +1916,7 @@
     </row>
     <row r="21" spans="1:9" ht="114">
       <c r="A21" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>166</v>
@@ -1930,10 +1931,10 @@
         <v>53</v>
       </c>
       <c r="F21" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>235</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>236</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
@@ -1949,16 +1950,16 @@
         <v>3</v>
       </c>
       <c r="D22" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>237</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>238</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
@@ -2382,13 +2383,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="F39" s="18" t="s">
         <v>242</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>12</v>
@@ -2516,7 +2517,7 @@
         <v>122</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G44" s="18" t="s">
         <v>123</v>
@@ -2658,7 +2659,7 @@
     </row>
     <row r="50" spans="1:10" ht="114">
       <c r="A50" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>194</v>
@@ -2763,7 +2764,7 @@
     </row>
     <row r="54" spans="1:10" ht="142.5">
       <c r="A54" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>198</v>

--- a/QCM4_1_CH.xlsx
+++ b/QCM4_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F1A8C9-C224-4BEB-A1F8-5AD44F2C4584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7130170D-7A1F-41CF-A839-99C245C92451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -802,7 +802,7 @@
     <t>La molécule suivante :
 R — OH
 &lt;br&gt; est :
-&lt;br&gt;\text{R}-\text{C}(=\text{O})-\text{O}-\text{R}' + \text{OH}^- \rightleftharpoons \text{R}-\text{C}(=\text{O})-\text{O}^- + \text{R}'-\text{OH}</t>
+&lt;br&gt;$\text{R}-\text{C}(=\text{O})-\text{O}-\text{R}' + \text{OH}^- \rightleftharpoons \text{R}-\text{C}(=\text{O})-\text{O}^- + \text{R}'-\text{OH}$</t>
   </si>
 </sst>
 </file>

--- a/QCM4_1_CH.xlsx
+++ b/QCM4_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7130170D-7A1F-41CF-A839-99C245C92451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF08FFA4-A6BB-434F-B0D5-CD16A73D7A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,8 +801,7 @@
   <si>
     <t>La molécule suivante :
 R — OH
-&lt;br&gt; est :
-&lt;br&gt;$\text{R}-\text{C}(=\text{O})-\text{O}-\text{R}' + \text{OH}^- \rightleftharpoons \text{R}-\text{C}(=\text{O})-\text{O}^- + \text{R}'-\text{OH}$</t>
+&lt;br&gt; est :</t>
   </si>
 </sst>
 </file>
